--- a/Prestador/neotin/resultado/relatorio_neotin_COMPLETO.xlsx
+++ b/Prestador/neotin/resultado/relatorio_neotin_COMPLETO.xlsx
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -637,13 +637,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1147,37 +1147,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>13</v>
       </c>
-      <c r="D17" t="n">
-        <v>9</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
